--- a/data/trans_orig/IP16B08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B08-Edad-trans_orig.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
